--- a/docs/Test_Report/Lin/TestPlanExecutionReport_Lin.xlsx
+++ b/docs/Test_Report/Lin/TestPlanExecutionReport_Lin.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Strategy Compliance'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <sz val="16"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -77,11 +77,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000000FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
@@ -104,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -136,13 +131,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -724,7 +716,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836,MCAL-30835</t>
+          <t>MCAL-32377,MCAL-32375</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -734,7 +726,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09 07:16:08.013348-05:00 CDT</t>
+          <t>2025-08-29 04:42:30.200826-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -806,12 +798,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -831,7 +823,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
     </row>
@@ -843,12 +835,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -880,12 +872,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1028,12 +1020,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1053,7 +1045,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1111,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1151,12 +1143,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1183,12 +1175,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>100%</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1362,7 +1354,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
@@ -1372,7 +1364,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="7" t="inlineStr">
@@ -1381,7 +1373,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
@@ -1391,7 +1383,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
@@ -1409,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U78"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1545,12 +1537,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1657,12 +1649,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1676,12 +1668,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1788,12 +1780,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1807,12 +1799,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1919,12 +1911,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1938,12 +1930,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2050,12 +2042,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -2069,12 +2061,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2181,12 +2173,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -2200,12 +2192,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2313,12 +2305,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2332,12 +2324,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2444,12 +2436,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2463,12 +2455,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2575,12 +2567,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2594,12 +2586,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2706,12 +2698,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2725,12 +2717,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2837,12 +2829,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2856,12 +2848,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2968,12 +2960,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -2987,12 +2979,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -3099,12 +3091,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -3118,12 +3110,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -3230,12 +3222,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -3249,12 +3241,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -3361,12 +3353,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -3380,12 +3372,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -3492,12 +3484,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -3511,12 +3503,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -3623,12 +3615,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -3642,12 +3634,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3757,12 +3749,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3776,12 +3768,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3890,12 +3882,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3909,12 +3901,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -4023,12 +4015,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -4042,12 +4034,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -4156,12 +4148,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -4175,12 +4167,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -4290,12 +4282,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -4309,12 +4301,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -4423,12 +4415,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -4442,12 +4434,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4556,12 +4548,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -4575,12 +4567,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -4690,12 +4682,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -4709,12 +4701,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4824,12 +4816,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -4843,12 +4835,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -4957,12 +4949,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -4976,12 +4968,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5090,12 +5082,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -5109,12 +5101,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -5224,12 +5216,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -5243,12 +5235,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5357,12 +5349,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -5376,12 +5368,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -5490,12 +5482,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -5509,12 +5501,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5623,12 +5615,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -5642,12 +5634,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -5756,12 +5748,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -5775,12 +5767,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5889,12 +5881,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -5908,12 +5900,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -6022,12 +6014,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -6041,12 +6033,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -6155,12 +6147,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -6174,12 +6166,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -6288,12 +6280,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -6307,12 +6299,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -6422,12 +6414,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -6441,12 +6433,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -6556,12 +6548,12 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -6575,12 +6567,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -6689,12 +6681,12 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -6708,12 +6700,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -6820,12 +6812,12 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
@@ -6839,12 +6831,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -6951,12 +6943,12 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -6970,12 +6962,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -7082,12 +7074,12 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
@@ -7101,12 +7093,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7213,12 +7205,12 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
@@ -7232,12 +7224,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -7345,12 +7337,12 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
@@ -7364,12 +7356,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -7477,12 +7469,12 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -7496,12 +7488,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -7608,12 +7600,12 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
@@ -7627,12 +7619,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -7739,12 +7731,12 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
@@ -7758,12 +7750,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -7870,12 +7862,12 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
@@ -7889,12 +7881,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -8001,12 +7993,12 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
@@ -8020,12 +8012,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30832</t>
+          <t>MCAL-32376</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Automated Tests</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -8132,12 +8124,12 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30836</t>
+          <t>MCAL-32377</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Automated Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Automated Test Run</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
@@ -8151,57 +8143,57 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29574</t>
+          <t>MCAL-32187</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>LIN Qualification : Lin Driver Safety Error checks</t>
+          <t>Lin SendData test : Transmit master response frame, slave response frame ans slave to slave response frame in loops</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28942,MCAL-28940,MCAL-28941,MCAL-28939,MCAL-28938,MCAL-28936,MCAL-28935,MCAL-28937</t>
+          <t>MCAL-25677</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>F29H85x-evm</t>
+          <t>F29H85x-evm,F29P58x-evm</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>The LIN driver should report safety related errors while transmission/reception</t>
+          <t>Transmit master response frame, slave response frame ans slave to slave response frame in loops</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>Manual Verification</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Required code should be covered</t>
+          <t>All LIN frames should be transmitted successfully</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -8221,7 +8213,7 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>Sanity</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -8231,240 +8223,240 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr"/>
       <c r="T52" s="3" t="inlineStr"/>
-      <c r="U52" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U52" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
+          <t>MCAL-29574</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>LIN Qualification : Lin Driver Safety Error checks</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-28942,MCAL-28940,MCAL-28941,MCAL-28939,MCAL-28938,MCAL-28936,MCAL-28935,MCAL-28937</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>The LIN driver should report safety related errors while transmission/reception</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Required code should be covered</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>Sanity</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>Lin</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32375</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32374</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
           <t>MCAL-28601</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Lin Test Send Frame Negative TXRX Busy </t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>MCAL-25566</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>Lin Test Send Frame Negative Slave TXRX Busy 
 Send slave response ID and immediately send master response.</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t>Driver should detect the fault and return Error</t>
         </is>
       </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>Fault Injection</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr">
+      <c r="M54" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N53" s="3" t="inlineStr">
+      <c r="N54" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
+      <c r="O54" s="3" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="P53" s="3" t="inlineStr">
+      <c r="P54" s="3" t="inlineStr">
         <is>
           <t>Lin</t>
         </is>
       </c>
-      <c r="Q53" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30835</t>
-        </is>
-      </c>
-      <c r="R53" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S53" s="3" t="inlineStr"/>
-      <c r="T53" s="3" t="inlineStr"/>
-      <c r="U53" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30834</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-28600</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Lin Test Checkwakeup LineCategory Coverage Test</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-25566</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>Lin Test Checkwakeup LineCategory Coverage Test</t>
-        </is>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>Driver should detect the wakeup Pulse</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N54" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="P54" s="3" t="inlineStr">
-        <is>
-          <t>Lin</t>
-        </is>
-      </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
       <c r="T54" s="3" t="inlineStr"/>
-      <c r="U54" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U54" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28448</t>
+          <t>MCAL-28600</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>LIN Performance test : Send Data Slave Response</t>
+          <t>Lin Test Checkwakeup LineCategory Coverage Test</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -8474,7 +8466,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25607</t>
+          <t>MCAL-25566</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -8489,7 +8481,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>LIN Performance test - Send Data For Slave response</t>
+          <t>Lin Test Checkwakeup LineCategory Coverage Test</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -8499,7 +8491,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>Should match performance expectations</t>
+          <t>Driver should detect the wakeup Pulse</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
@@ -8519,7 +8511,7 @@
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>Sanity</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
@@ -8529,51 +8521,51 @@
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr"/>
       <c r="T55" s="3" t="inlineStr"/>
-      <c r="U55" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U55" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27500</t>
+          <t>MCAL-28448</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>LIN Qualification : MCAL shall support Lin_GetStatus API</t>
+          <t>LIN Performance test : Send Data Slave Response</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement,Requirement,Requirement</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24752,MCAL-24731,MCAL-24760,MCAL-24751</t>
+          <t>MCAL-25607</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -8583,12 +8575,12 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Fault Operation : The LIN Driver shall provide a status for error events on the bus.</t>
+          <t>LIN Performance test - Send Data For Slave response</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -8598,7 +8590,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Required code should be covered</t>
+          <t>Should match performance expectations</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -8628,51 +8620,51 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
       <c r="T56" s="3" t="inlineStr"/>
-      <c r="U56" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U56" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27499</t>
+          <t>MCAL-27500</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>LIN Qualification : MCAL shall support Lin_SendFrame API</t>
+          <t>LIN Qualification : MCAL shall support Lin_GetStatus API</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
+          <t>Requirement,Requirement,Requirement,Requirement</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24748,MCAL-24752,MCAL-28941,MCAL-28935,MCAL-28938,MCAL-28937,MCAL-28936,MCAL-28940,MCAL-24731,MCAL-24730,MCAL-28939,MCAL-24751</t>
+          <t>MCAL-24752,MCAL-24731,MCAL-24760,MCAL-24751</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -8687,7 +8679,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>The LIN driver shall have an API which the driver shall use to poll for transmit / receive notifications. It should support all modes of data transfer, Master response, Slave response and Slave to Slave.</t>
+          <t>Fault Operation : The LIN Driver shall provide a status for error events on the bus.</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -8727,51 +8719,51 @@
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr"/>
       <c r="T57" s="3" t="inlineStr"/>
-      <c r="U57" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U57" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27498</t>
+          <t>MCAL-27499</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>LIN Qualification : MCAL shall support Lin_WakeupInternal API</t>
+          <t>LIN Qualification : MCAL shall support Lin_SendFrame API</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24732</t>
+          <t>MCAL-24748,MCAL-24752,MCAL-28941,MCAL-28935,MCAL-28938,MCAL-28937,MCAL-28936,MCAL-28940,MCAL-24731,MCAL-24730,MCAL-28939,MCAL-24751</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -8786,7 +8778,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Lin should support wakepup from internal sleep</t>
+          <t>The LIN driver shall have an API which the driver shall use to poll for transmit / receive notifications. It should support all modes of data transfer, Master response, Slave response and Slave to Slave.</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -8826,240 +8818,240 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr"/>
       <c r="T58" s="3" t="inlineStr"/>
-      <c r="U58" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U58" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
+          <t>MCAL-27498</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>LIN Qualification : MCAL shall support Lin_WakeupInternal API</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-24732</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Lin should support wakepup from internal sleep</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Required code should be covered</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>Sanity</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>Lin</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32375</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32374</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
           <t>MCAL-27497</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>LIN Qualification : MCAL shall support Lin_Wakeup API</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>MCAL-24732</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>Qualification</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>If a wakeup occurs during transition to sleep-mode, this channel shall go back to the running mode
 Lin B Int 0 RTINT CAT1</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
         <is>
           <t>Required code should be covered</t>
         </is>
       </c>
-      <c r="L59" s="3" t="inlineStr">
+      <c r="L60" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M59" s="3" t="inlineStr">
+      <c r="M60" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N59" s="3" t="inlineStr">
+      <c r="N60" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
+      <c r="O60" s="3" t="inlineStr">
         <is>
           <t>Sanity</t>
         </is>
       </c>
-      <c r="P59" s="3" t="inlineStr">
+      <c r="P60" s="3" t="inlineStr">
         <is>
           <t>Lin</t>
         </is>
       </c>
-      <c r="Q59" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30835</t>
-        </is>
-      </c>
-      <c r="R59" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S59" s="3" t="inlineStr"/>
-      <c r="T59" s="3" t="inlineStr"/>
-      <c r="U59" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30834</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27496</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>LIN Qualification : MCAL shall support Lin_GoToSleep API</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>Requirement,Requirement</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-24758,MCAL-24759</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>ShutDown Operations : Transition to sleep-mode shall be handled</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>Required code should be covered</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N60" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>Sanity</t>
-        </is>
-      </c>
-      <c r="P60" s="3" t="inlineStr">
-        <is>
-          <t>Lin</t>
-        </is>
-      </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr"/>
       <c r="T60" s="3" t="inlineStr"/>
-      <c r="U60" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U60" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27495</t>
+          <t>MCAL-27496</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>LIN Qualification : MCAL shall support Lin_GoToSleepInternal API</t>
+          <t>LIN Qualification : MCAL shall support Lin_GoToSleep API</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -9069,7 +9061,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24759,MCAL-24758</t>
+          <t>MCAL-24758,MCAL-24759</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -9084,7 +9076,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>The LIN Driver shall be able to put the LIN hardware to a reduced power operation mode if needed</t>
+          <t>ShutDown Operations : Transition to sleep-mode shall be handled</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -9124,51 +9116,51 @@
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr"/>
       <c r="T61" s="3" t="inlineStr"/>
-      <c r="U61" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U61" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27494</t>
+          <t>MCAL-27495</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>LIN Qualification : MCAL shall support Lin_CheckWakeup API</t>
+          <t>LIN Qualification : MCAL shall support Lin_GoToSleepInternal API</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Requirement,Requirement</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24756</t>
+          <t>MCAL-24759,MCAL-24758</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -9183,7 +9175,7 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>Normal Operation : The LIN Driver shall provide a notification for wake-up events</t>
+          <t>The LIN Driver shall be able to put the LIN hardware to a reduced power operation mode if needed</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -9223,64 +9215,163 @@
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr"/>
       <c r="T62" s="3" t="inlineStr"/>
-      <c r="U62" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U62" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
+          <t>MCAL-27494</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>LIN Qualification : MCAL shall support Lin_CheckWakeup API</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-24756</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Normal Operation : The LIN Driver shall provide a notification for wake-up events</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Required code should be covered</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>Sanity</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>Lin</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32375</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32374</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
           <t>MCAL-27493</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>LIN Qualification : MCAL shall support Lin_Init API</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>MCAL-24750,MCAL-24729,MCAL-24755,MCAL-24754,MCAL-24728,MCAL-24753,MCAL-24757</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>Qualification</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>Initialization : The LIN Driver shall support the initialization of each LIN channel separately
 The LIN Driver shall support dynamic selection of 
@@ -9288,187 +9379,88 @@
 One LIN driver shall be able to handle more than one LIN channel</t>
         </is>
       </c>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K63" s="3" t="inlineStr">
+      <c r="K64" s="3" t="inlineStr">
         <is>
           <t>Required code should be covered</t>
         </is>
       </c>
-      <c r="L63" s="3" t="inlineStr">
+      <c r="L64" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M63" s="3" t="inlineStr">
+      <c r="M64" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N63" s="3" t="inlineStr">
+      <c r="N64" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
+      <c r="O64" s="3" t="inlineStr">
         <is>
           <t>Sanity</t>
         </is>
       </c>
-      <c r="P63" s="3" t="inlineStr">
+      <c r="P64" s="3" t="inlineStr">
         <is>
           <t>Lin</t>
         </is>
       </c>
-      <c r="Q63" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30835</t>
-        </is>
-      </c>
-      <c r="R63" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S63" s="3" t="inlineStr"/>
-      <c r="T63" s="3" t="inlineStr"/>
-      <c r="U63" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30834</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27492</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>LIN Qualification : Lin Functional Requirement specification verification test</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>Requirement,Requirement</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-28200,MCAL-24749</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>Lin Functional Requirement specification verification test</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>Required code should be covered</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N64" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>Sanity</t>
-        </is>
-      </c>
-      <c r="P64" s="3" t="inlineStr">
-        <is>
-          <t>Lin</t>
-        </is>
-      </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr"/>
       <c r="T64" s="3" t="inlineStr"/>
-      <c r="U64" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U64" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27491</t>
+          <t>MCAL-27492</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>LIN BSW and SPAL Requirements verification</t>
+          <t>LIN Qualification : Lin Functional Requirement specification verification test</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture</t>
+          <t>Requirement,Requirement</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-12327,MCAL-12315,MCAL-12340,MCAL-12359,MCAL-12421,MCAL-12427,MCAL-12341,MCAL-12307,MCAL-12345,MCAL-12391,MCAL-12326,MCAL-12338,MCAL-12414,MCAL-12438,MCAL-12393,MCAL-12362,MCAL-12394,MCAL-12372,MCAL-12376,MCAL-12343,MCAL-12378,MCAL-12342,MCAL-12426,MCAL-12412,MCAL-12329,MCAL-12373,MCAL-12344,MCAL-12308,MCAL-12388,MCAL-12411,MCAL-12346,MCAL-12385,MCAL-12387,MCAL-12353,MCAL-12375,MCAL-12435,MCAL-12354,MCAL-12434,MCAL-12424,MCAL-12347,MCAL-12323,MCAL-12416,MCAL-12306,MCAL-12356,MCAL-12358,MCAL-12374,MCAL-12415,MCAL-12304,MCAL-12377,MCAL-12339</t>
+          <t>MCAL-28200,MCAL-24749</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -9478,12 +9470,12 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>LIN BSW and SPAL Requirements verification</t>
+          <t>Lin Functional Requirement specification verification test</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -9523,51 +9515,51 @@
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr"/>
       <c r="T65" s="3" t="inlineStr"/>
-      <c r="U65" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U65" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27490</t>
+          <t>MCAL-27491</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>LIN Stress Test</t>
+          <t>LIN BSW and SPAL Requirements verification</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
+          <t>Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25554,MCAL-25633,MCAL-25627,MCAL-25634,MCAL-25623,MCAL-25624,MCAL-25631,MCAL-25632,MCAL-25625,MCAL-25556,MCAL-25579,MCAL-25626</t>
+          <t>MCAL-12327,MCAL-12315,MCAL-12340,MCAL-12359,MCAL-12421,MCAL-12427,MCAL-12341,MCAL-12307,MCAL-12345,MCAL-12391,MCAL-12326,MCAL-12338,MCAL-12414,MCAL-12438,MCAL-12393,MCAL-12362,MCAL-12394,MCAL-12372,MCAL-12376,MCAL-12343,MCAL-12378,MCAL-12342,MCAL-12426,MCAL-12412,MCAL-12329,MCAL-12373,MCAL-12344,MCAL-12308,MCAL-12388,MCAL-12411,MCAL-12346,MCAL-12385,MCAL-12387,MCAL-12353,MCAL-12375,MCAL-12435,MCAL-12354,MCAL-12434,MCAL-12424,MCAL-12347,MCAL-12323,MCAL-12416,MCAL-12306,MCAL-12356,MCAL-12358,MCAL-12374,MCAL-12415,MCAL-12304,MCAL-12377,MCAL-12339</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -9577,12 +9569,12 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>LIN Stress Test - Sleep Wakeup Send Data</t>
+          <t>LIN BSW and SPAL Requirements verification</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -9592,7 +9584,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>Sleep wakup happen without issue</t>
+          <t>Required code should be covered</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -9622,51 +9614,51 @@
       </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr"/>
       <c r="T66" s="3" t="inlineStr"/>
-      <c r="U66" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U66" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27489</t>
+          <t>MCAL-27490</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>LIN Performance test : Send Data Master Response</t>
+          <t>LIN Stress Test</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
+          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25610,MCAL-25566,MCAL-25570,MCAL-25571,MCAL-25572,MCAL-25609,MCAL-25613,MCAL-25614,MCAL-25560,MCAL-25561,MCAL-25569,MCAL-25559,MCAL-25573,MCAL-25564,MCAL-25574,MCAL-25563,MCAL-25565,MCAL-25568,MCAL-25567,MCAL-25562,MCAL-25607,MCAL-25608,MCAL-25611,MCAL-25612,MCAL-25606</t>
+          <t>MCAL-25554,MCAL-25633,MCAL-25627,MCAL-25634,MCAL-25623,MCAL-25624,MCAL-25631,MCAL-25632,MCAL-25625,MCAL-25556,MCAL-25579,MCAL-25626</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -9681,7 +9673,7 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>LIN Performance test - Send Data</t>
+          <t>LIN Stress Test - Sleep Wakeup Send Data</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -9691,7 +9683,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>Should match performance expectations</t>
+          <t>Sleep wakup happen without issue</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
@@ -9721,51 +9713,51 @@
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr"/>
       <c r="T67" s="3" t="inlineStr"/>
-      <c r="U67" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U67" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27483</t>
+          <t>MCAL-27489</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>LinSetLoopbackModeCoverageCase1 - DISABLED LOOPBACK</t>
+          <t>LIN Performance test : Send Data Master Response</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25687,MCAL-25692</t>
+          <t>MCAL-25610,MCAL-25566,MCAL-25570,MCAL-25571,MCAL-25572,MCAL-25609,MCAL-25613,MCAL-25614,MCAL-25560,MCAL-25561,MCAL-25569,MCAL-25559,MCAL-25573,MCAL-25564,MCAL-25574,MCAL-25563,MCAL-25565,MCAL-25568,MCAL-25567,MCAL-25562,MCAL-25607,MCAL-25608,MCAL-25611,MCAL-25612,MCAL-25606</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -9780,7 +9772,7 @@
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Lin SetLoopbackMode CoverageCase1</t>
+          <t>LIN Performance test - Send Data</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -9790,7 +9782,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>Required code should be covered</t>
+          <t>Should match performance expectations</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -9810,7 +9802,7 @@
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Sanity</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
@@ -9820,69 +9812,168 @@
       </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr"/>
       <c r="T68" s="3" t="inlineStr"/>
-      <c r="U68" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U68" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
+          <t>MCAL-27483</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>LinSetLoopbackModeCoverageCase1 - DISABLED LOOPBACK</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Design,Design</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-25687,MCAL-25692</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Lin SetLoopbackMode CoverageCase1</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Required code should be covered</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>Lin</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32375</t>
+        </is>
+      </c>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr"/>
+      <c r="T69" s="3" t="inlineStr"/>
+      <c r="U69" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32374</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
           <t>MCAL-27454</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Lin Test Wake Up Main test case</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>MCAL-25679,MCAL-25555,MCAL-25557,MCAL-25671,MCAL-25578,MCAL-25699,MCAL-25698,MCAL-25673,MCAL-25696</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>Lin Test Wake Up Main test case</t>
         </is>
       </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -9919,172 +10010,73 @@
 }</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
+      <c r="K70" s="3" t="inlineStr">
         <is>
           <t>Lin Should send wakeup command</t>
         </is>
       </c>
-      <c r="L69" s="3" t="inlineStr">
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M69" s="3" t="inlineStr">
+      <c r="M70" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N69" s="3" t="inlineStr">
+      <c r="N70" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O69" s="3" t="inlineStr">
+      <c r="O70" s="3" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="P69" s="3" t="inlineStr">
+      <c r="P70" s="3" t="inlineStr">
         <is>
           <t>Lin</t>
         </is>
       </c>
-      <c r="Q69" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30835</t>
-        </is>
-      </c>
-      <c r="R69" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S69" s="3" t="inlineStr"/>
-      <c r="T69" s="3" t="inlineStr"/>
-      <c r="U69" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30834</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27453</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Lin SendData test LinTestSlaveResponseMainCase</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-25560,MCAL-25565,MCAL-25569,MCAL-25572,MCAL-25607,MCAL-25609,MCAL-25675,MCAL-25636,MCAL-25567,MCAL-25568,MCAL-25574,MCAL-25606,MCAL-25683,MCAL-25635,MCAL-25610,MCAL-25638,MCAL-25562,MCAL-25559,MCAL-25678,MCAL-25573,MCAL-25637,MCAL-25563,MCAL-25608,MCAL-25698,MCAL-25673,MCAL-25688,MCAL-25696</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>Lin SendData test LinTestSlaveResponseMainCase</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>Received data shall be equal to transmitted data at given baud rate</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M70" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N70" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
-          <t>Sanity</t>
-        </is>
-      </c>
-      <c r="P70" s="3" t="inlineStr">
-        <is>
-          <t>Lin</t>
-        </is>
-      </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr"/>
       <c r="T70" s="3" t="inlineStr"/>
-      <c r="U70" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U70" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27452</t>
+          <t>MCAL-27453</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Lin SendData test LinTestMasterResponseMainCase</t>
+          <t>Lin SendData test LinTestSlaveResponseMainCase</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -10094,7 +10086,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25559,MCAL-25566,MCAL-25570,MCAL-25571,MCAL-25637,MCAL-25683,MCAL-25636,MCAL-25609,MCAL-25610,MCAL-25638,MCAL-25564,MCAL-25568,MCAL-25574,MCAL-25607,MCAL-25608,MCAL-25635,MCAL-25560,MCAL-25561,MCAL-25563,MCAL-25567,MCAL-25606,MCAL-25673,MCAL-25696,MCAL-25698,MCAL-25674,MCAL-25688,MCAL-25677</t>
+          <t>MCAL-25560,MCAL-25565,MCAL-25569,MCAL-25572,MCAL-25607,MCAL-25609,MCAL-25675,MCAL-25636,MCAL-25567,MCAL-25568,MCAL-25574,MCAL-25606,MCAL-25683,MCAL-25635,MCAL-25610,MCAL-25638,MCAL-25562,MCAL-25559,MCAL-25678,MCAL-25573,MCAL-25637,MCAL-25563,MCAL-25608,MCAL-25698,MCAL-25673,MCAL-25688,MCAL-25696</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -10109,7 +10101,7 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Lin SendData test LinTestMasterResponseMainCase</t>
+          <t>Lin SendData test LinTestSlaveResponseMainCase</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -10149,69 +10141,168 @@
       </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr"/>
       <c r="T71" s="3" t="inlineStr"/>
-      <c r="U71" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U71" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
+          <t>MCAL-27452</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Lin SendData test LinTestMasterResponseMainCase</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-25559,MCAL-25566,MCAL-25570,MCAL-25571,MCAL-25637,MCAL-25683,MCAL-25636,MCAL-25609,MCAL-25610,MCAL-25638,MCAL-25564,MCAL-25568,MCAL-25574,MCAL-25607,MCAL-25608,MCAL-25635,MCAL-25560,MCAL-25561,MCAL-25563,MCAL-25567,MCAL-25606,MCAL-25673,MCAL-25696,MCAL-25698,MCAL-25674,MCAL-25688,MCAL-25677</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Lin SendData test LinTestMasterResponseMainCase</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Received data shall be equal to transmitted data at given baud rate</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>Sanity</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>Lin</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32375</t>
+        </is>
+      </c>
+      <c r="R72" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr"/>
+      <c r="T72" s="3" t="inlineStr"/>
+      <c r="U72" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32374</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
           <t>MCAL-27451</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Lin Test GoToSleep Main Case</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>MCAL-25615,MCAL-25617,MCAL-25619,MCAL-25642,MCAL-25662,MCAL-25699,MCAL-25553,MCAL-25558,MCAL-25552,MCAL-25575,MCAL-25576,MCAL-25616,MCAL-25680,MCAL-25620,MCAL-25618,MCAL-25681,MCAL-25673,MCAL-25696,MCAL-25698,MCAL-25689,MCAL-25690</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I72" s="3" t="inlineStr">
+      <c r="I73" s="3" t="inlineStr">
         <is>
           <t>Lin Test GoToSleep Main Case</t>
         </is>
       </c>
-      <c r="J72" s="3" t="inlineStr">
+      <c r="J73" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -10248,282 +10339,183 @@
 }</t>
         </is>
       </c>
-      <c r="K72" s="3" t="inlineStr">
+      <c r="K73" s="3" t="inlineStr">
         <is>
           <t>Module should go to sleep state</t>
         </is>
       </c>
-      <c r="L72" s="3" t="inlineStr">
+      <c r="L73" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M72" s="3" t="inlineStr">
+      <c r="M73" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N72" s="3" t="inlineStr">
+      <c r="N73" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O72" s="3" t="inlineStr">
+      <c r="O73" s="3" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="P72" s="3" t="inlineStr">
+      <c r="P73" s="3" t="inlineStr">
         <is>
           <t>Lin</t>
         </is>
       </c>
-      <c r="Q72" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30835</t>
-        </is>
-      </c>
-      <c r="R72" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S72" s="3" t="inlineStr"/>
-      <c r="T72" s="3" t="inlineStr"/>
-      <c r="U72" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30834</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="Q73" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32375</t>
+        </is>
+      </c>
+      <c r="R73" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
+        </is>
+      </c>
+      <c r="S73" s="3" t="inlineStr"/>
+      <c r="T73" s="3" t="inlineStr"/>
+      <c r="U73" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32374</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>MCAL-27450</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>LinTestCheckWakeupMainCase</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>MCAL-25577,MCAL-25682,MCAL-25685,MCAL-25542,MCAL-25543,MCAL-25670,MCAL-25642,MCAL-25643,MCAL-25644,MCAL-25601,MCAL-25696,MCAL-25698,MCAL-25691,MCAL-25541</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">LIN CheckWakeup test case, With Interrupt Enabled
 Lin A line 0 CAT2 </t>
         </is>
       </c>
-      <c r="J73" s="3" t="inlineStr">
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K73" s="3" t="inlineStr">
+      <c r="K74" s="3" t="inlineStr">
         <is>
           <t>Should verify if a wakeup has occurred on the addressed LIN channel.</t>
         </is>
       </c>
-      <c r="L73" s="3" t="inlineStr">
+      <c r="L74" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M73" s="3" t="inlineStr">
+      <c r="M74" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N73" s="3" t="inlineStr">
+      <c r="N74" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O73" s="3" t="inlineStr">
+      <c r="O74" s="3" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="P73" s="3" t="inlineStr">
+      <c r="P74" s="3" t="inlineStr">
         <is>
           <t>Lin</t>
         </is>
       </c>
-      <c r="Q73" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30835</t>
-        </is>
-      </c>
-      <c r="R73" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S73" s="3" t="inlineStr"/>
-      <c r="T73" s="3" t="inlineStr"/>
-      <c r="U73" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30834</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27448</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>LIN Integration: Data types validation</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>Architecture,Design,Architecture,Design,Design,Architecture,Architecture,Architecture,Design,Design,Design,Design,Architecture,Architecture</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-25190,MCAL-25592,MCAL-25191,MCAL-25590,MCAL-25690,MCAL-25192,MCAL-25194,MCAL-25195,MCAL-25691,MCAL-25591,MCAL-25689,MCAL-25688,MCAL-25189,MCAL-25193</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>Verify Autosar and device specific types used in lin driver</t>
-        </is>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>Verify Lin_ConfigType, Lin_FramePidType , Lin_FrameCsModelType , Lin_FrameResponseType,Lin_FrameDlType,Lin_PduType, Lin_StatusType, and other device dpecific data types used</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N74" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O74" s="3" t="inlineStr">
-        <is>
-          <t>Sanity</t>
-        </is>
-      </c>
-      <c r="P74" s="3" t="inlineStr">
-        <is>
-          <t>Lin</t>
-        </is>
-      </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr"/>
       <c r="T74" s="3" t="inlineStr"/>
-      <c r="U74" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U74" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27447</t>
+          <t>MCAL-27448</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>LIN Integration : Container configurations validation</t>
+          <t>LIN Integration: Data types validation</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Architecture,Design,Architecture,Design,Design,Architecture,Architecture,Architecture,Design,Design,Design,Design,Architecture,Architecture</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25205</t>
+          <t>MCAL-25190,MCAL-25592,MCAL-25191,MCAL-25590,MCAL-25690,MCAL-25192,MCAL-25194,MCAL-25195,MCAL-25691,MCAL-25591,MCAL-25689,MCAL-25688,MCAL-25189,MCAL-25193</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -10538,7 +10530,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Verify Lin Containers are as per autosar specification</t>
+          <t>Verify Autosar and device specific types used in lin driver</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -10548,7 +10540,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>The Lin module file structure has been developed as per SWS_Lin_00075</t>
+          <t>Verify Lin_ConfigType, Lin_FramePidType , Lin_FrameCsModelType , Lin_FrameResponseType,Lin_FrameDlType,Lin_PduType, Lin_StatusType, and other device dpecific data types used</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
@@ -10578,51 +10570,51 @@
       </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr"/>
       <c r="T75" s="3" t="inlineStr"/>
-      <c r="U75" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U75" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27446</t>
+          <t>MCAL-27447</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>LIN Integration: File Structure Validation</t>
+          <t>LIN Integration : Container configurations validation</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Design,Design,Design,Design,Design,Design,Architecture,Design,Design,Design,Design,Architecture,Architecture,Architecture,Architecture,Design,Architecture,Architecture</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25189,MCAL-25530,MCAL-25533,MCAL-25534,MCAL-25535,MCAL-25538,MCAL-25540,MCAL-25190,MCAL-25531,MCAL-25532,MCAL-25537,MCAL-25539,MCAL-28233,MCAL-25191,MCAL-25192,MCAL-25194,MCAL-25536,MCAL-25193,MCAL-25195</t>
+          <t>MCAL-25205</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -10637,7 +10629,7 @@
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>Develop the Lin module file structure as per SWS_Lin_00075</t>
+          <t>Verify Lin Containers are as per autosar specification</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -10677,51 +10669,51 @@
       </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr"/>
       <c r="T76" s="3" t="inlineStr"/>
-      <c r="U76" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U76" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27445</t>
+          <t>MCAL-27446</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>LIN Integration : MCAL shall support Lin_GetStatus API</t>
+          <t>LIN Integration: File Structure Validation</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Architecture</t>
+          <t>Architecture,Design,Design,Design,Design,Design,Design,Architecture,Design,Design,Design,Design,Architecture,Architecture,Architecture,Architecture,Design,Architecture,Architecture</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25195,MCAL-25204</t>
+          <t>MCAL-25189,MCAL-25530,MCAL-25533,MCAL-25534,MCAL-25535,MCAL-25538,MCAL-25540,MCAL-25190,MCAL-25531,MCAL-25532,MCAL-25537,MCAL-25539,MCAL-28233,MCAL-25191,MCAL-25192,MCAL-25194,MCAL-25536,MCAL-25193,MCAL-25195</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -10736,7 +10728,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Write and verify functionality of Lin_GetStatus API in Lin module</t>
+          <t>Develop the Lin module file structure as per SWS_Lin_00075</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -10746,7 +10738,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>Lin_GetStatus API has been supported by MCAL LIN driver</t>
+          <t>The Lin module file structure has been developed as per SWS_Lin_00075</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
@@ -10776,124 +10768,223 @@
       </c>
       <c r="Q77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30835</t>
+          <t>MCAL-32375</t>
         </is>
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr"/>
       <c r="T77" s="3" t="inlineStr"/>
-      <c r="U77" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U77" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30834</t>
+          <t>MCAL-32374</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : LIN - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
+          <t>MCAL-27445</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>LIN Integration : MCAL shall support Lin_GetStatus API</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Architecture,Architecture</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-25195,MCAL-25204</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>Write and verify functionality of Lin_GetStatus API in Lin module</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>Lin_GetStatus API has been supported by MCAL LIN driver</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>Sanity</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>Lin</t>
+        </is>
+      </c>
+      <c r="Q78" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32375</t>
+        </is>
+      </c>
+      <c r="R78" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
+        </is>
+      </c>
+      <c r="S78" s="3" t="inlineStr"/>
+      <c r="T78" s="3" t="inlineStr"/>
+      <c r="U78" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32374</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : LIN - Manual Tests</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
           <t>MCAL-27438</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>LIN Integration : MCAL shall support Lin_CheckWakeup API</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>Architecture</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>MCAL-25197</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="I79" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Write and verify functionality of Lin_CheckWakeup API in Lin Module.
 Lin B CAT1 Line 1 </t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>Manual verification</t>
         </is>
       </c>
-      <c r="K78" s="3" t="inlineStr">
+      <c r="K79" s="3" t="inlineStr">
         <is>
           <t>Lin_CheckWakeup API has been supported by MCAL LIN driver</t>
         </is>
       </c>
-      <c r="L78" s="3" t="inlineStr">
+      <c r="L79" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M78" s="3" t="inlineStr">
+      <c r="M79" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N78" s="3" t="inlineStr">
+      <c r="N79" s="3" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="O78" s="3" t="inlineStr">
+      <c r="O79" s="3" t="inlineStr">
         <is>
           <t>Sanity</t>
         </is>
       </c>
-      <c r="P78" s="3" t="inlineStr">
+      <c r="P79" s="3" t="inlineStr">
         <is>
           <t>Lin</t>
         </is>
       </c>
-      <c r="Q78" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30835</t>
-        </is>
-      </c>
-      <c r="R78" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01 : Lin - Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S78" s="3" t="inlineStr"/>
-      <c r="T78" s="3" t="inlineStr"/>
-      <c r="U78" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="Q79" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-32375</t>
+        </is>
+      </c>
+      <c r="R79" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.03.00 : Lin - Manual Test Run</t>
+        </is>
+      </c>
+      <c r="S79" s="3" t="inlineStr"/>
+      <c r="T79" s="3" t="inlineStr"/>
+      <c r="U79" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U78"/>
+  <autoFilter ref="A1:U79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10942,12 +11033,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Test Plan</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Test Plan Key</t>
         </is>
@@ -10969,8 +11060,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="n"/>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Test Plan Name</t>
         </is>
@@ -10992,8 +11083,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n"/>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="A4" s="11" t="n"/>
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Test Case Key</t>
         </is>
@@ -11015,8 +11106,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Test Case Name</t>
         </is>
@@ -11038,8 +11129,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n"/>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Associated Issue(s) Type</t>
         </is>
@@ -11066,8 +11157,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Associated Issue(s) ID(s)</t>
         </is>
@@ -11089,8 +11180,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Test Platform</t>
         </is>
@@ -11112,8 +11203,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Test Level</t>
         </is>
@@ -11129,7 +11220,7 @@
 -- "Not Provided" if no 'Test Scope' is provided in Jira</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11141,8 +11232,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Test Description</t>
         </is>
@@ -11164,8 +11255,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Test Setup</t>
         </is>
@@ -11187,8 +11278,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Pass/Fail Criteria</t>
         </is>
@@ -11210,8 +11301,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
@@ -11222,7 +11313,7 @@
 (Map Test Method from Qmetry)</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11234,15 +11325,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="13" t="n"/>
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="12" t="n"/>
       <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Functional:
 Tests covering functional requirements-based  aspects of the software</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11254,8 +11345,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="13" t="n"/>
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="12" t="n"/>
       <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Compatability:
@@ -11263,7 +11354,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing that measures the degree to which a test item can function satisfactorily alongside other independent products in a shared environment (co-existence), and where necessary, exchanges information with other systems or components (interoperability)</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11275,15 +11366,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="13" t="n"/>
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="12" t="n"/>
       <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Usability:
 Test Case covers usability/api/look and feel aspects of the module including out-of box (OOB) experience</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11295,15 +11386,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="13" t="n"/>
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="12" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Fault Injection:
 Testing based on injection of errors or faults to ensure no unintended consequences</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11315,8 +11406,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="13" t="n"/>
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="12" t="n"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Performance: 
@@ -11324,7 +11415,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the degree to which a test item accomplishes its designated functions within given constraints of time and other resources</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11336,8 +11427,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="13" t="n"/>
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="12" t="n"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Reliability: 
@@ -11345,7 +11436,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the ability of a test item to perform its required functions, including evaluating the frequency with which failures occur, when it is used under stated conditions for a specified period of time</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11357,8 +11448,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="13" t="n"/>
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="12" t="n"/>
       <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Stress:
@@ -11366,7 +11457,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of performance efficiency testing conducted to evaluate a test item's behaviour under conditions of loading above anticipated or specified capacity requirements, or of resource availability below minimum specified requirements</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11378,8 +11469,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="13" t="n"/>
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="12" t="n"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Security:
@@ -11387,7 +11478,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the degree to which a test item, and associated data and information, are protected so that unauthorized persons or systems cannot use, read, or modify them, and authorized persons or systems are not denied access to them</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11399,8 +11490,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="13" t="n"/>
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="12" t="n"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Maintainability:
@@ -11408,7 +11499,7 @@
 ISO/IEC/IEEE 29119-1 Defn: test type conducted to evaluate the degree of effectiveness and efficiency with which a test item may be modified</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11420,8 +11511,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="13" t="n"/>
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="12" t="n"/>
       <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Portability:
@@ -11429,7 +11520,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the ease with which a test item can be transferred from one hardware or software environment to another, including the level of modification needed for it to be executed in various types of environment</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11441,8 +11532,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Test Design Technique</t>
         </is>
@@ -11454,7 +11545,7 @@
 (Map Test Derivation Method from Qmetry)</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11466,8 +11557,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n"/>
-      <c r="B25" s="13" t="n"/>
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="12" t="n"/>
       <c r="C25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Requirements-Analysis:
@@ -11475,7 +11566,7 @@
 </t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11487,15 +11578,15 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="13" t="n"/>
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="12" t="n"/>
       <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Boundary Value Analysis:
 Test cases that apply to interfaces and values approaching and crossing the boundaries and out of range values</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11507,15 +11598,15 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n"/>
-      <c r="B27" s="13" t="n"/>
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="12" t="n"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Error Guessing:
 Test cases established based on lessons learned and expert judgement to determine situations that may cause software failures or errors to appear</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11527,28 +11618,28 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="13" t="n"/>
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="12" t="n"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Other (Use case analysis; Customer Usage; Requirement analysis; Failure Mode analysis):
 Teams are encouraged to use techniques defined by standards such as ISO/IEC/IEEE 29119-4; which needs to be refelcted within Qmetry</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n"/>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Test Execution Type</t>
         </is>
@@ -11558,7 +11649,7 @@
           <t>Identifies whether the case is automated or manually or Semi-Automated executed</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11570,8 +11661,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Test Category</t>
         </is>
@@ -11581,7 +11672,7 @@
           <t>Test Categories represent sets of tests that are commonly used.</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11593,15 +11684,15 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n"/>
-      <c r="B31" s="13" t="n"/>
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="12" t="n"/>
       <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Sanity:
 This Test case is identified to run for Sanity Checks. These are mainly the basic tests that need to be run as part of entry to validate phase</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11613,15 +11704,15 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="13" t="n"/>
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="12" t="n"/>
       <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Full:
 This category means running all test cases for identified releases</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11633,15 +11724,15 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n"/>
-      <c r="B33" s="13" t="n"/>
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="12" t="n"/>
       <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Base Regression:
 This Test case is identified to run for the Base Regression / maintenance releases</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -11653,8 +11744,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="n"/>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Test Component(s)</t>
         </is>
@@ -11664,24 +11755,24 @@
           <t xml:space="preserve">The field provides the Component(s) (in Jira) to which the Test Case is mapped to. </t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>Test Execution</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Build/Release Key</t>
         </is>
@@ -11703,8 +11794,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="n"/>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Defect Key</t>
         </is>
@@ -11726,8 +11817,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="n"/>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Defect Summary</t>
         </is>
@@ -11749,8 +11840,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="n"/>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Overall Status</t>
         </is>
@@ -11773,8 +11864,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="n"/>
-      <c r="B39" s="13" t="n"/>
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="12" t="n"/>
       <c r="C39" s="3" t="inlineStr">
         <is>
           <t>PASS
@@ -11793,8 +11884,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="n"/>
-      <c r="B40" s="13" t="n"/>
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="12" t="n"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
           <t>FAIL
@@ -11813,8 +11904,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="n"/>
-      <c r="B41" s="13" t="n"/>
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="12" t="n"/>
       <c r="C41" s="3" t="inlineStr">
         <is>
           <t>BLOCKED
@@ -11833,8 +11924,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="n"/>
-      <c r="B42" s="13" t="n"/>
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="12" t="n"/>
       <c r="C42" s="3" t="inlineStr">
         <is>
           <t>WIP
